--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix B2C-B2B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumen'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'P&amp;L Año 1'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Proyección 3 años'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mix B2C-B2B'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'KPIs'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -535,7 +541,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -562,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -618,7 +625,7 @@
       </c>
       <c r="E6" s="7">
         <f>D6/$D$21</f>
-        <v/>
+        <v>0.017450404114621603</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -643,7 +650,7 @@
       </c>
       <c r="E7" s="7">
         <f>D7/$D$21</f>
-        <v/>
+        <v>0.0440852314474651</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -668,7 +675,7 @@
       </c>
       <c r="E8" s="7">
         <f>D8/$D$21</f>
-        <v/>
+        <v>0.02351212343864805</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -693,7 +700,7 @@
       </c>
       <c r="E9" s="7">
         <f>D9/$D$21</f>
-        <v/>
+        <v>0.0707200587803086</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -718,7 +725,7 @@
       </c>
       <c r="E10" s="7">
         <f>D10/$D$21</f>
-        <v/>
+        <v>0.0881704628949302</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -743,7 +750,7 @@
       </c>
       <c r="E11" s="7">
         <f>D11/$D$21</f>
-        <v/>
+        <v>0.0707200587803086</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -768,7 +775,7 @@
       </c>
       <c r="E12" s="7">
         <f>D12/$D$21</f>
-        <v/>
+        <v>0.0266348273328435</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -793,7 +800,7 @@
       </c>
       <c r="E13" s="7">
         <f>D13/$D$21</f>
-        <v/>
+        <v>0.07714915503306392</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -818,7 +825,7 @@
       </c>
       <c r="E14" s="7">
         <f>D14/$D$21</f>
-        <v/>
+        <v>0.04041146216017634</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -843,7 +850,7 @@
       </c>
       <c r="E15" s="7">
         <f>D15/$D$21</f>
-        <v/>
+        <v>0.04371785451873622</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -868,7 +875,7 @@
       </c>
       <c r="E16" s="7">
         <f>D16/$D$21</f>
-        <v/>
+        <v>0.05878030859662013</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -893,7 +900,7 @@
       </c>
       <c r="E17" s="7">
         <f>D17/$D$21</f>
-        <v/>
+        <v>0.02351212343864805</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -918,7 +925,7 @@
       </c>
       <c r="E18" s="7">
         <f>D18/$D$21</f>
-        <v/>
+        <v>0.0881704628949302</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -943,7 +950,7 @@
       </c>
       <c r="E19" s="7">
         <f>D19/$D$21</f>
-        <v/>
+        <v>0.06980161645848641</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -968,7 +975,7 @@
       </c>
       <c r="E20" s="7">
         <f>D20/$D$21</f>
-        <v/>
+        <v>0.2571638501102131</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -984,15 +991,15 @@
       </c>
       <c r="B21" s="9">
         <f>SUM(B6:B20)</f>
-        <v/>
+        <v>8520.0</v>
       </c>
       <c r="C21" s="9">
         <f>SUM(C6:C20)</f>
-        <v/>
+        <v>21410.0</v>
       </c>
       <c r="D21" s="9">
         <f>SUM(D6:D20)</f>
-        <v/>
+        <v>54440.0</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
@@ -1003,11 +1010,20 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1015,7 +1031,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1050,6 +1066,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1166,7 +1183,7 @@
       </c>
       <c r="N5" s="12">
         <f>SUM(B5:M5)</f>
-        <v/>
+        <v>167200.0</v>
       </c>
     </row>
     <row r="6">
@@ -1213,7 +1230,7 @@
       </c>
       <c r="N6" s="12">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>436500.0</v>
       </c>
     </row>
     <row r="7">
@@ -1224,57 +1241,58 @@
       </c>
       <c r="B7" s="14">
         <f>SUM(B5:B6)</f>
-        <v/>
+        <v>17900.0</v>
       </c>
       <c r="C7" s="14">
         <f>SUM(C5:C6)</f>
-        <v/>
+        <v>22400.0</v>
       </c>
       <c r="D7" s="14">
         <f>SUM(D5:D6)</f>
-        <v/>
+        <v>35800.0</v>
       </c>
       <c r="E7" s="14">
         <f>SUM(E5:E6)</f>
-        <v/>
+        <v>42500.0</v>
       </c>
       <c r="F7" s="14">
         <f>SUM(F5:F6)</f>
-        <v/>
+        <v>64800.0</v>
       </c>
       <c r="G7" s="14">
         <f>SUM(G5:G6)</f>
-        <v/>
+        <v>78200.0</v>
       </c>
       <c r="H7" s="14">
         <f>SUM(H5:H6)</f>
-        <v/>
+        <v>62500.0</v>
       </c>
       <c r="I7" s="14">
         <f>SUM(I5:I6)</f>
-        <v/>
+        <v>35700.0</v>
       </c>
       <c r="J7" s="14">
         <f>SUM(J5:J6)</f>
-        <v/>
+        <v>60300.0</v>
       </c>
       <c r="K7" s="14">
         <f>SUM(K5:K6)</f>
-        <v/>
+        <v>62600.0</v>
       </c>
       <c r="L7" s="14">
         <f>SUM(L5:L6)</f>
-        <v/>
+        <v>44800.0</v>
       </c>
       <c r="M7" s="14">
         <f>SUM(M5:M6)</f>
-        <v/>
+        <v>76200.0</v>
       </c>
       <c r="N7" s="14">
         <f>SUM(N5:N6)</f>
-        <v/>
-      </c>
-    </row>
+        <v>603700.0</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -1283,55 +1301,55 @@
       </c>
       <c r="B9" s="12">
         <f>B7*0.28</f>
-        <v/>
+        <v>5012.000000000001</v>
       </c>
       <c r="C9" s="12">
         <f>C7*0.28</f>
-        <v/>
+        <v>6272.000000000001</v>
       </c>
       <c r="D9" s="12">
         <f>D7*0.28</f>
-        <v/>
+        <v>10024.000000000002</v>
       </c>
       <c r="E9" s="12">
         <f>E7*0.28</f>
-        <v/>
+        <v>11900.000000000002</v>
       </c>
       <c r="F9" s="12">
         <f>F7*0.28</f>
-        <v/>
+        <v>18144.0</v>
       </c>
       <c r="G9" s="12">
         <f>G7*0.28</f>
-        <v/>
+        <v>21896.000000000004</v>
       </c>
       <c r="H9" s="12">
         <f>H7*0.28</f>
-        <v/>
+        <v>17500.0</v>
       </c>
       <c r="I9" s="12">
         <f>I7*0.28</f>
-        <v/>
+        <v>9996.000000000002</v>
       </c>
       <c r="J9" s="12">
         <f>J7*0.28</f>
-        <v/>
+        <v>16884.0</v>
       </c>
       <c r="K9" s="12">
         <f>K7*0.28</f>
-        <v/>
+        <v>17528.0</v>
       </c>
       <c r="L9" s="12">
         <f>L7*0.28</f>
-        <v/>
+        <v>12544.000000000002</v>
       </c>
       <c r="M9" s="12">
         <f>M7*0.28</f>
-        <v/>
+        <v>21336.000000000004</v>
       </c>
       <c r="N9" s="12">
         <f>N7*0.28</f>
-        <v/>
+        <v>169036.00000000003</v>
       </c>
     </row>
     <row r="10">
@@ -1342,55 +1360,55 @@
       </c>
       <c r="B10" s="12">
         <f>B7*0.05</f>
-        <v/>
+        <v>895.0</v>
       </c>
       <c r="C10" s="12">
         <f>C7*0.05</f>
-        <v/>
+        <v>1120.0</v>
       </c>
       <c r="D10" s="12">
         <f>D7*0.05</f>
-        <v/>
+        <v>1790.0</v>
       </c>
       <c r="E10" s="12">
         <f>E7*0.05</f>
-        <v/>
+        <v>2125.0</v>
       </c>
       <c r="F10" s="12">
         <f>F7*0.05</f>
-        <v/>
+        <v>3240.0</v>
       </c>
       <c r="G10" s="12">
         <f>G7*0.05</f>
-        <v/>
+        <v>3910.0</v>
       </c>
       <c r="H10" s="12">
         <f>H7*0.05</f>
-        <v/>
+        <v>3125.0</v>
       </c>
       <c r="I10" s="12">
         <f>I7*0.05</f>
-        <v/>
+        <v>1785.0</v>
       </c>
       <c r="J10" s="12">
         <f>J7*0.05</f>
-        <v/>
+        <v>3015.0</v>
       </c>
       <c r="K10" s="12">
         <f>K7*0.05</f>
-        <v/>
+        <v>3130.0</v>
       </c>
       <c r="L10" s="12">
         <f>L7*0.05</f>
-        <v/>
+        <v>2240.0</v>
       </c>
       <c r="M10" s="12">
         <f>M7*0.05</f>
-        <v/>
+        <v>3810.0</v>
       </c>
       <c r="N10" s="12">
         <f>N7*0.05</f>
-        <v/>
+        <v>30185.0</v>
       </c>
     </row>
     <row r="11">
@@ -1401,57 +1419,58 @@
       </c>
       <c r="B11" s="12">
         <f>B7*0.15</f>
-        <v/>
+        <v>2685.0</v>
       </c>
       <c r="C11" s="12">
         <f>C7*0.15</f>
-        <v/>
+        <v>3360.0</v>
       </c>
       <c r="D11" s="12">
         <f>D7*0.15</f>
-        <v/>
+        <v>5370.0</v>
       </c>
       <c r="E11" s="12">
         <f>E7*0.15</f>
-        <v/>
+        <v>6375.0</v>
       </c>
       <c r="F11" s="12">
         <f>F7*0.15</f>
-        <v/>
+        <v>9720.0</v>
       </c>
       <c r="G11" s="12">
         <f>G7*0.15</f>
-        <v/>
+        <v>11730.0</v>
       </c>
       <c r="H11" s="12">
         <f>H7*0.15</f>
-        <v/>
+        <v>9375.0</v>
       </c>
       <c r="I11" s="12">
         <f>I7*0.15</f>
-        <v/>
+        <v>5355.0</v>
       </c>
       <c r="J11" s="12">
         <f>J7*0.15</f>
-        <v/>
+        <v>9045.0</v>
       </c>
       <c r="K11" s="12">
         <f>K7*0.15</f>
-        <v/>
+        <v>9390.0</v>
       </c>
       <c r="L11" s="12">
         <f>L7*0.15</f>
-        <v/>
+        <v>6720.0</v>
       </c>
       <c r="M11" s="12">
         <f>M7*0.15</f>
-        <v/>
+        <v>11430.0</v>
       </c>
       <c r="N11" s="12">
         <f>N7*0.15</f>
-        <v/>
-      </c>
-    </row>
+        <v>90555.0</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1496,7 +1515,7 @@
       </c>
       <c r="N13" s="12">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>960.0</v>
       </c>
     </row>
     <row r="14">
@@ -1543,7 +1562,7 @@
       </c>
       <c r="N14" s="12">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>1680.0</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1609,7 @@
       </c>
       <c r="N15" s="12">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>3360.0</v>
       </c>
     </row>
     <row r="16">
@@ -1637,9 +1656,10 @@
       </c>
       <c r="N16" s="12">
         <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
+        <v>4560.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -1648,55 +1668,55 @@
       </c>
       <c r="B18" s="14">
         <f>SUM(B9:B11)+SUM(B13:B16)</f>
-        <v/>
+        <v>9472.0</v>
       </c>
       <c r="C18" s="14">
         <f>SUM(C9:C11)+SUM(C13:C16)</f>
-        <v/>
+        <v>11632.0</v>
       </c>
       <c r="D18" s="14">
         <f>SUM(D9:D11)+SUM(D13:D16)</f>
-        <v/>
+        <v>18064.0</v>
       </c>
       <c r="E18" s="14">
         <f>SUM(E9:E11)+SUM(E13:E16)</f>
-        <v/>
+        <v>21280.0</v>
       </c>
       <c r="F18" s="14">
         <f>SUM(F9:F11)+SUM(F13:F16)</f>
-        <v/>
+        <v>31984.0</v>
       </c>
       <c r="G18" s="14">
         <f>SUM(G9:G11)+SUM(G13:G16)</f>
-        <v/>
+        <v>38416.0</v>
       </c>
       <c r="H18" s="14">
         <f>SUM(H9:H11)+SUM(H13:H16)</f>
-        <v/>
+        <v>30880.0</v>
       </c>
       <c r="I18" s="14">
         <f>SUM(I9:I11)+SUM(I13:I16)</f>
-        <v/>
+        <v>18016.0</v>
       </c>
       <c r="J18" s="14">
         <f>SUM(J9:J11)+SUM(J13:J16)</f>
-        <v/>
+        <v>29824.0</v>
       </c>
       <c r="K18" s="14">
         <f>SUM(K9:K11)+SUM(K13:K16)</f>
-        <v/>
+        <v>30928.0</v>
       </c>
       <c r="L18" s="14">
         <f>SUM(L9:L11)+SUM(L13:L16)</f>
-        <v/>
+        <v>22384.0</v>
       </c>
       <c r="M18" s="14">
         <f>SUM(M9:M11)+SUM(M13:M16)</f>
-        <v/>
+        <v>37456.0</v>
       </c>
       <c r="N18" s="14">
         <f>SUM(N9:N11)+SUM(N13:N16)</f>
-        <v/>
+        <v>300336.0</v>
       </c>
     </row>
     <row r="19">
@@ -1707,63 +1727,72 @@
       </c>
       <c r="B19" s="15">
         <f>B7-B18</f>
-        <v/>
+        <v>8428.0</v>
       </c>
       <c r="C19" s="15">
         <f>C7-C18</f>
-        <v/>
+        <v>10768.0</v>
       </c>
       <c r="D19" s="15">
         <f>D7-D18</f>
-        <v/>
+        <v>17736.0</v>
       </c>
       <c r="E19" s="15">
         <f>E7-E18</f>
-        <v/>
+        <v>21220.0</v>
       </c>
       <c r="F19" s="15">
         <f>F7-F18</f>
-        <v/>
+        <v>32816.0</v>
       </c>
       <c r="G19" s="15">
         <f>G7-G18</f>
-        <v/>
+        <v>39784.0</v>
       </c>
       <c r="H19" s="15">
         <f>H7-H18</f>
-        <v/>
+        <v>31620.0</v>
       </c>
       <c r="I19" s="15">
         <f>I7-I18</f>
-        <v/>
+        <v>17684.0</v>
       </c>
       <c r="J19" s="15">
         <f>J7-J18</f>
-        <v/>
+        <v>30476.0</v>
       </c>
       <c r="K19" s="15">
         <f>K7-K18</f>
-        <v/>
+        <v>31672.0</v>
       </c>
       <c r="L19" s="15">
         <f>L7-L18</f>
-        <v/>
+        <v>22416.0</v>
       </c>
       <c r="M19" s="15">
         <f>M7-M18</f>
-        <v/>
+        <v>38744.0</v>
       </c>
       <c r="N19" s="15">
         <f>N7-N18</f>
-        <v/>
+        <v>303364.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1771,7 +1800,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1796,6 +1825,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1890,15 +1920,15 @@
       </c>
       <c r="B9" s="6">
         <f>B5*B7</f>
-        <v/>
+        <v>167200.0</v>
       </c>
       <c r="C9" s="6">
         <f>C5*C7</f>
-        <v/>
+        <v>235620.0</v>
       </c>
       <c r="D9" s="6">
         <f>D5*D7</f>
-        <v/>
+        <v>314600.0</v>
       </c>
     </row>
     <row r="10">
@@ -1909,15 +1939,15 @@
       </c>
       <c r="B10" s="6">
         <f>B6*B8</f>
-        <v/>
+        <v>436500.0</v>
       </c>
       <c r="C10" s="6">
         <f>C6*C8</f>
-        <v/>
+        <v>611100.0</v>
       </c>
       <c r="D10" s="6">
         <f>D6*D8</f>
-        <v/>
+        <v>800800.0</v>
       </c>
     </row>
     <row r="11">
@@ -1928,15 +1958,15 @@
       </c>
       <c r="B11" s="9">
         <f>B9+B10</f>
-        <v/>
+        <v>603700.0</v>
       </c>
       <c r="C11" s="9">
         <f>C9+C10</f>
-        <v/>
+        <v>846720.0</v>
       </c>
       <c r="D11" s="9">
         <f>D9+D10</f>
-        <v/>
+        <v>1115400.0</v>
       </c>
     </row>
     <row r="12">
@@ -1947,15 +1977,15 @@
       </c>
       <c r="B12" s="6">
         <f>B11*0.28</f>
-        <v/>
+        <v>169036.00000000003</v>
       </c>
       <c r="C12" s="6">
         <f>C11*0.26</f>
-        <v/>
+        <v>220147.2</v>
       </c>
       <c r="D12" s="6">
         <f>D11*0.25</f>
-        <v/>
+        <v>278850.0</v>
       </c>
     </row>
     <row r="13">
@@ -1966,15 +1996,15 @@
       </c>
       <c r="B13" s="6">
         <f>B11*0.05</f>
-        <v/>
+        <v>30185.0</v>
       </c>
       <c r="C13" s="6">
         <f>C11*0.05</f>
-        <v/>
+        <v>42336.0</v>
       </c>
       <c r="D13" s="6">
         <f>D11*0.05</f>
-        <v/>
+        <v>55770.0</v>
       </c>
     </row>
     <row r="14">
@@ -1985,15 +2015,15 @@
       </c>
       <c r="B14" s="6">
         <f>B11*0.15</f>
-        <v/>
+        <v>90555.0</v>
       </c>
       <c r="C14" s="6">
         <f>C11*0.14</f>
-        <v/>
+        <v>118540.80000000002</v>
       </c>
       <c r="D14" s="6">
         <f>D11*0.13</f>
-        <v/>
+        <v>145002.0</v>
       </c>
     </row>
     <row r="15">
@@ -2020,15 +2050,15 @@
       </c>
       <c r="B16" s="9">
         <f>SUM(B12:B15)</f>
-        <v/>
+        <v>300336.0</v>
       </c>
       <c r="C16" s="9">
         <f>SUM(C12:C15)</f>
-        <v/>
+        <v>393224.0</v>
       </c>
       <c r="D16" s="9">
         <f>SUM(D12:D15)</f>
-        <v/>
+        <v>494022.0</v>
       </c>
     </row>
     <row r="17">
@@ -2039,15 +2069,15 @@
       </c>
       <c r="B17" s="17">
         <f>B11-B16</f>
-        <v/>
+        <v>303364.0</v>
       </c>
       <c r="C17" s="17">
         <f>C11-C16</f>
-        <v/>
+        <v>453496.0</v>
       </c>
       <c r="D17" s="17">
         <f>D11-D16</f>
-        <v/>
+        <v>621378.0</v>
       </c>
     </row>
     <row r="18">
@@ -2058,23 +2088,32 @@
       </c>
       <c r="B18" s="19">
         <f>B17/B11</f>
-        <v/>
+        <v>0.5025078681464303</v>
       </c>
       <c r="C18" s="19">
         <f>C17/C11</f>
-        <v/>
+        <v>0.5355914588057445</v>
       </c>
       <c r="D18" s="19">
         <f>D17/D11</f>
-        <v/>
+        <v>0.5570898332436794</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2082,7 +2121,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2105,6 +2144,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2135,7 +2175,7 @@
       </c>
       <c r="B6" s="6">
         <f>2200*0.35+4500*0.65</f>
-        <v/>
+        <v>3695.0</v>
       </c>
     </row>
     <row r="7">
@@ -2146,7 +2186,7 @@
       </c>
       <c r="B7" s="7">
         <f>1-0.28-0.05-0.15</f>
-        <v/>
+        <v>0.5199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2157,7 +2197,7 @@
       </c>
       <c r="B8" s="6">
         <f>B6*B7</f>
-        <v/>
+        <v>1921.3999999999996</v>
       </c>
     </row>
     <row r="9">
@@ -2168,7 +2208,7 @@
       </c>
       <c r="B9" s="20">
         <f>B5/B8</f>
-        <v/>
+        <v>5.495992505464766</v>
       </c>
     </row>
     <row r="10">
@@ -2179,15 +2219,24 @@
       </c>
       <c r="B10" s="21">
         <f>B9/12</f>
-        <v/>
+        <v>0.4579993754553972</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2195,7 +2244,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2222,6 +2271,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2536,10 +2586,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2547,7 +2606,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2572,6 +2631,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2812,9 +2872,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>